--- a/data/publications/monthly-rbi-bulletin/external-sector/table-38-external-commercial-borrowings-ecbs-registrations.xlsx
+++ b/data/publications/monthly-rbi-bulletin/external-sector/table-38-external-commercial-borrowings-ecbs-registrations.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="217">
   <si>
     <t>Month/ Year</t>
   </si>
@@ -886,7 +886,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -969,9 +969,6 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="1" fillId="2" borderId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="right" vertical="center"/>
     </xf>
@@ -15902,7 +15899,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH28"/>
+  <dimension ref="A1:AH29"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="10.7125106666667" customWidth="1"/>
@@ -17969,107 +17966,211 @@
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="22.3986" customHeight="1">
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="23">
         <v>139</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="23">
         <v>5943</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="23">
         <v>1</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="23">
         <v>133</v>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="23">
         <v>140</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="23">
         <v>6076</v>
       </c>
-      <c r="I28" s="28">
+      <c r="I28" s="23">
         <v>4.3</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="23">
         <v>1.24</v>
       </c>
-      <c r="K28" s="27" t="s">
+      <c r="K28" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="11">
         <v>25</v>
       </c>
-      <c r="M28" s="13">
+      <c r="M28" s="11">
         <v>453</v>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="11">
         <v>1808</v>
       </c>
-      <c r="O28" s="13">
+      <c r="O28" s="11">
         <v>133</v>
       </c>
-      <c r="P28" s="13">
+      <c r="P28" s="11">
         <v>1551</v>
       </c>
-      <c r="Q28" s="13">
-        <v>0</v>
-      </c>
-      <c r="R28" s="13">
-        <v>0</v>
-      </c>
-      <c r="S28" s="13">
+      <c r="Q28" s="11">
+        <v>0</v>
+      </c>
+      <c r="R28" s="11">
+        <v>0</v>
+      </c>
+      <c r="S28" s="11">
         <v>124</v>
       </c>
-      <c r="T28" s="13">
-        <v>0</v>
-      </c>
-      <c r="U28" s="13">
-        <v>0</v>
-      </c>
-      <c r="V28" s="13">
+      <c r="T28" s="11">
+        <v>0</v>
+      </c>
+      <c r="U28" s="11">
+        <v>0</v>
+      </c>
+      <c r="V28" s="11">
         <v>100</v>
       </c>
-      <c r="W28" s="13">
+      <c r="W28" s="11">
         <v>1628</v>
       </c>
-      <c r="X28" s="13">
+      <c r="X28" s="11">
         <v>1995</v>
       </c>
-      <c r="Y28" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="13">
+      <c r="Y28" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="11">
         <v>1973</v>
       </c>
-      <c r="AA28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="13">
+      <c r="AA28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="11">
         <v>22</v>
       </c>
-      <c r="AC28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="13">
+      <c r="AC28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="11">
         <v>67</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="22.3986" customHeight="1">
+      <c r="B29" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="25">
+        <v>171</v>
+      </c>
+      <c r="D29" s="25">
+        <v>6917</v>
+      </c>
+      <c r="E29" s="25">
+        <v>6</v>
+      </c>
+      <c r="F29" s="25">
+        <v>780</v>
+      </c>
+      <c r="G29" s="25">
+        <v>177</v>
+      </c>
+      <c r="H29" s="25">
+        <v>7697</v>
+      </c>
+      <c r="I29" s="25">
+        <v>4.5</v>
+      </c>
+      <c r="J29" s="25">
+        <v>1.59</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="L29" s="26">
+        <v>0</v>
+      </c>
+      <c r="M29" s="26">
+        <v>1252</v>
+      </c>
+      <c r="N29" s="26">
+        <v>2141</v>
+      </c>
+      <c r="O29" s="26">
+        <v>474</v>
+      </c>
+      <c r="P29" s="26">
+        <v>1340</v>
+      </c>
+      <c r="Q29" s="26">
+        <v>0</v>
+      </c>
+      <c r="R29" s="26">
+        <v>0</v>
+      </c>
+      <c r="S29" s="26">
+        <v>1</v>
+      </c>
+      <c r="T29" s="26">
+        <v>325</v>
+      </c>
+      <c r="U29" s="26">
+        <v>1</v>
+      </c>
+      <c r="V29" s="26">
+        <v>50</v>
+      </c>
+      <c r="W29" s="26">
+        <v>527</v>
+      </c>
+      <c r="X29" s="26">
+        <v>2996</v>
+      </c>
+      <c r="Y29" s="26">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="26">
+        <v>2996</v>
+      </c>
+      <c r="AA29" s="26">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="26">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="26">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="26">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="26">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="26">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="26">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="26">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="26">
+        <v>731</v>
       </c>
     </row>
   </sheetData>
@@ -18107,12 +18208,12 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="20.7987" customHeight="1">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="1.0666" customHeight="1"/>
     <row r="6" s="1" customFormat="1" ht="58.1297" customHeight="1">
@@ -18134,7 +18235,7 @@
       <c r="I6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="28" t="s">
         <v>5</v>
       </c>
       <c r="K6" s="14" t="s">
@@ -18686,67 +18787,67 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="20.7987" customHeight="1">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="1.0666" customHeight="1"/>
     <row r="6" s="1" customFormat="1" ht="58.1297" customHeight="1">
       <c r="B6" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31" t="s">
+      <c r="D6" s="30"/>
+      <c r="E6" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31" t="s">
+      <c r="F6" s="30"/>
+      <c r="G6" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="31"/>
+      <c r="H6" s="30"/>
       <c r="I6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="28" t="s">
         <v>5</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="32"/>
-      <c r="AG6" s="32"/>
-      <c r="AH6" s="32"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="31"/>
+      <c r="AH6" s="31"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="66.6625" customHeight="1">
       <c r="B7" s="2"/>
@@ -18873,7 +18974,7 @@
       <c r="J8" s="10">
         <v>1.48</v>
       </c>
-      <c r="K8" s="33" t="s">
+      <c r="K8" s="32" t="s">
         <v>185</v>
       </c>
       <c r="L8" s="10">
@@ -19489,68 +19590,68 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="20.7987" customHeight="1">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="1.0666" customHeight="1"/>
     <row r="6" s="1" customFormat="1" ht="58.1297" customHeight="1">
       <c r="B6" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31" t="s">
+      <c r="D6" s="30"/>
+      <c r="E6" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31" t="s">
+      <c r="F6" s="30"/>
+      <c r="G6" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="31"/>
+      <c r="H6" s="30"/>
       <c r="I6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="28" t="s">
         <v>5</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="32"/>
-      <c r="AG6" s="32"/>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="32"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="31"/>
+      <c r="AH6" s="31"/>
+      <c r="AI6" s="31"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="66.6625" customHeight="1">
       <c r="B7" s="2"/>
@@ -19680,7 +19781,7 @@
       <c r="J8" s="10">
         <v>1.5</v>
       </c>
-      <c r="K8" s="33" t="s">
+      <c r="K8" s="32" t="s">
         <v>90</v>
       </c>
       <c r="L8" s="10">
